--- a/xls/square_16_tri3_17.xlsx
+++ b/xls/square_16_tri3_17.xlsx
@@ -482,13 +482,13 @@
         <v>1734</v>
       </c>
       <c r="I17">
-        <v>-0.7212383954068645</v>
+        <v>-0.7212377287059236</v>
       </c>
       <c r="J17">
-        <v>-2.1077665176881277</v>
+        <v>-2.1077665392814264</v>
       </c>
       <c r="K17">
-        <v>1.1554805484158406</v>
+        <v>1.1554846841831738</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -517,13 +517,13 @@
         <v>1944</v>
       </c>
       <c r="I18">
-        <v>-2.501502595905351</v>
+        <v>-2.5015031956038802</v>
       </c>
       <c r="J18">
-        <v>-2.105682533961712</v>
+        <v>-2.105682978572616</v>
       </c>
       <c r="K18">
-        <v>0.3647268914143822</v>
+        <v>0.36471494386795594</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -552,13 +552,13 @@
         <v>2166</v>
       </c>
       <c r="I19">
-        <v>-2.4788563815788263</v>
+        <v>-2.478855699454717</v>
       </c>
       <c r="J19">
-        <v>-2.0598588892436984</v>
+        <v>-2.059858784017596</v>
       </c>
       <c r="K19">
-        <v>1.2055407378845646</v>
+        <v>1.2055409799235672</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -587,13 +587,13 @@
         <v>2400</v>
       </c>
       <c r="I20">
-        <v>-2.0076832796610904</v>
+        <v>-2.0076818682976656</v>
       </c>
       <c r="J20">
-        <v>-1.552180214083298</v>
+        <v>-1.5521799322296934</v>
       </c>
       <c r="K20">
-        <v>2.527765936321421</v>
+        <v>2.5277659248839135</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -622,13 +622,13 @@
         <v>2646</v>
       </c>
       <c r="I21">
-        <v>-1.7543712311430426</v>
+        <v>-1.7543711394574328</v>
       </c>
       <c r="J21">
-        <v>-1.4306735132007007</v>
+        <v>-1.4306734791383542</v>
       </c>
       <c r="K21">
-        <v>2.8678811543114517</v>
+        <v>2.867881126535096</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -657,13 +657,13 @@
         <v>2904</v>
       </c>
       <c r="I22">
-        <v>-0.9346888140606984</v>
+        <v>-0.934688914620678</v>
       </c>
       <c r="J22">
-        <v>-0.6895721509807086</v>
+        <v>-0.6895722033603224</v>
       </c>
       <c r="K22">
-        <v>3.594892383576049</v>
+        <v>3.5948924035498737</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -692,13 +692,13 @@
         <v>3174</v>
       </c>
       <c r="I23">
-        <v>-0.46783440186554287</v>
+        <v>-0.46783439789582526</v>
       </c>
       <c r="J23">
-        <v>-0.42538090814695584</v>
+        <v>-0.4253809047600321</v>
       </c>
       <c r="K23">
-        <v>3.8684454506637</v>
+        <v>3.8684454484707116</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -727,13 +727,13 @@
         <v>3456</v>
       </c>
       <c r="I24">
-        <v>-0.010867284645070372</v>
+        <v>-0.010867284856613705</v>
       </c>
       <c r="J24">
-        <v>-0.00872749183057581</v>
+        <v>-0.008727491914345508</v>
       </c>
       <c r="K24">
-        <v>3.3684637253337772</v>
+        <v>3.3684637231809726</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -762,13 +762,13 @@
         <v>3750</v>
       </c>
       <c r="I25">
-        <v>0.0010831698917782467</v>
+        <v>0.00108316990666433</v>
       </c>
       <c r="J25">
-        <v>-6.705958545615817e-5</v>
+        <v>-6.705957938969819e-5</v>
       </c>
       <c r="K25">
-        <v>2.975958726015146</v>
+        <v>2.975958726749069</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -797,13 +797,13 @@
         <v>4056</v>
       </c>
       <c r="I26">
-        <v>0.0009538306081825108</v>
+        <v>0.0009538306252046159</v>
       </c>
       <c r="J26">
-        <v>0.0001809416697315379</v>
+        <v>0.0001809416754526302</v>
       </c>
       <c r="K26">
-        <v>2.8360611896103656</v>
+        <v>2.8360611932246713</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -832,13 +832,13 @@
         <v>4374</v>
       </c>
       <c r="I27">
-        <v>0.0006896177197074843</v>
+        <v>0.0006896177170145399</v>
       </c>
       <c r="J27">
-        <v>0.00017520176954393624</v>
+        <v>0.0001752017686853562</v>
       </c>
       <c r="K27">
-        <v>2.7246303853069644</v>
+        <v>2.7246303840732518</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -867,13 +867,13 @@
         <v>4704</v>
       </c>
       <c r="I28">
-        <v>0.0003707095670072234</v>
+        <v>0.0003707095676602869</v>
       </c>
       <c r="J28">
-        <v>9.910584826048194e-5</v>
+        <v>9.910584846950044e-5</v>
       </c>
       <c r="K28">
-        <v>2.592719219308398</v>
+        <v>2.5927192199589375</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -902,13 +902,13 @@
         <v>5046</v>
       </c>
       <c r="I29">
-        <v>0.00014256437286089223</v>
+        <v>0.0001425643728678331</v>
       </c>
       <c r="J29">
-        <v>2.3121542400754232e-5</v>
+        <v>2.3121542419943326e-5</v>
       </c>
       <c r="K29">
-        <v>2.4908807222347766</v>
+        <v>2.4908807221981757</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -937,13 +937,13 @@
         <v>5400</v>
       </c>
       <c r="I30">
-        <v>4.301609272652843e-5</v>
+        <v>4.3016092958136946e-5</v>
       </c>
       <c r="J30">
-        <v>-2.6287808597889913e-5</v>
+        <v>-2.6287808533758253e-5</v>
       </c>
       <c r="K30">
-        <v>2.496789417782633</v>
+        <v>2.496789418348063</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -972,13 +972,13 @@
         <v>5766</v>
       </c>
       <c r="I31">
-        <v>4.2579008075242034e-5</v>
+        <v>4.257900812210375e-5</v>
       </c>
       <c r="J31">
-        <v>-3.337637723885204e-5</v>
+        <v>-3.337637721657437e-5</v>
       </c>
       <c r="K31">
-        <v>2.516985731774672</v>
+        <v>2.5169857319670252</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -1007,13 +1007,13 @@
         <v>6144</v>
       </c>
       <c r="I32">
-        <v>6.660429443392765e-5</v>
+        <v>6.66042941485305e-5</v>
       </c>
       <c r="J32">
-        <v>-1.7946223784592315e-5</v>
+        <v>-1.7946223854798255e-5</v>
       </c>
       <c r="K32">
-        <v>2.493231391019335</v>
+        <v>2.493231390190656</v>
       </c>
     </row>
   </sheetData>

--- a/xls/square_16_tri3_17.xlsx
+++ b/xls/square_16_tri3_17.xlsx
@@ -456,6 +456,76 @@
         <v>10</v>
       </c>
     </row>
+    <row r="15" spans="1:11">
+      <c r="A15" t="s">
+        <v>11</v>
+      </c>
+      <c r="B15">
+        <v>324</v>
+      </c>
+      <c r="C15" t="s">
+        <v>11</v>
+      </c>
+      <c r="D15">
+        <v>289</v>
+      </c>
+      <c r="E15" t="s">
+        <v>12</v>
+      </c>
+      <c r="F15">
+        <v>256</v>
+      </c>
+      <c r="G15" t="s">
+        <v>13</v>
+      </c>
+      <c r="H15">
+        <v>1350</v>
+      </c>
+      <c r="I15">
+        <v>3.0064607921417865</v>
+      </c>
+      <c r="J15">
+        <v>-0.31318613103137977</v>
+      </c>
+      <c r="K15">
+        <v>0.8722197113984638</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="A16" t="s">
+        <v>11</v>
+      </c>
+      <c r="B16">
+        <v>324</v>
+      </c>
+      <c r="C16" t="s">
+        <v>11</v>
+      </c>
+      <c r="D16">
+        <v>289</v>
+      </c>
+      <c r="E16" t="s">
+        <v>12</v>
+      </c>
+      <c r="F16">
+        <v>289</v>
+      </c>
+      <c r="G16" t="s">
+        <v>13</v>
+      </c>
+      <c r="H16">
+        <v>1536</v>
+      </c>
+      <c r="I16">
+        <v>1.9870095716045504</v>
+      </c>
+      <c r="J16">
+        <v>-1.0416968380858511</v>
+      </c>
+      <c r="K16">
+        <v>0.3020504114702844</v>
+      </c>
+    </row>
     <row r="17" spans="1:11">
       <c r="A17" t="s">
         <v>11</v>
